--- a/research/traditional_assets/database/data/estonia/estonia_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_electronics_general.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.22</v>
+        <v>-0.6662983425414364</v>
       </c>
       <c r="H2">
-        <v>-0.22</v>
+        <v>-0.6751381215469613</v>
       </c>
       <c r="I2">
-        <v>-3.19</v>
+        <v>-0.8364640883977901</v>
       </c>
       <c r="J2">
-        <v>-3.19</v>
+        <v>-0.8364640883977901</v>
       </c>
       <c r="K2">
-        <v>-0.327</v>
+        <v>-0.863</v>
       </c>
       <c r="L2">
-        <v>-3.27</v>
+        <v>-0.9535911602209944</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.972</v>
+        <v>0.323</v>
       </c>
       <c r="V2">
-        <v>0.09084112149532711</v>
+        <v>0.05676625659050966</v>
+      </c>
+      <c r="W2">
+        <v>-0.9442013129102844</v>
       </c>
       <c r="X2">
-        <v>0.07693205798252749</v>
+        <v>0.1340078015242971</v>
+      </c>
+      <c r="Y2">
+        <v>-1.078209114434582</v>
       </c>
       <c r="AB2">
-        <v>0.07670751935730633</v>
+        <v>0.1308060524157124</v>
       </c>
       <c r="AD2">
-        <v>0.051</v>
+        <v>0.228</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.051</v>
+        <v>0.228</v>
       </c>
       <c r="AG2">
-        <v>-0.9209999999999999</v>
+        <v>-0.095</v>
       </c>
       <c r="AH2">
-        <v>0.004743744767928565</v>
+        <v>0.03852652923284894</v>
       </c>
       <c r="AI2">
-        <v>0.05284974093264248</v>
+        <v>0.1289592760180996</v>
       </c>
       <c r="AJ2">
-        <v>-0.09418140914203905</v>
+        <v>-0.01697944593386953</v>
       </c>
       <c r="AK2">
-        <v>131.5714285714305</v>
+        <v>-0.06574394463667819</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AM2">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AN2">
-        <v>-0.1895910780669145</v>
+        <v>-0.3019867549668874</v>
       </c>
       <c r="AO2">
-        <v>-53.16666666666666</v>
+        <v>-68.81818181818183</v>
       </c>
       <c r="AP2">
-        <v>3.423791821561338</v>
+        <v>0.1258278145695364</v>
       </c>
       <c r="AQ2">
-        <v>-53.16666666666666</v>
+        <v>-68.81818181818183</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.22</v>
+        <v>-0.6662983425414364</v>
       </c>
       <c r="H3">
-        <v>-0.22</v>
+        <v>-0.6751381215469613</v>
       </c>
       <c r="I3">
-        <v>-3.19</v>
+        <v>-0.8364640883977901</v>
       </c>
       <c r="J3">
-        <v>-3.19</v>
+        <v>-0.8364640883977901</v>
       </c>
       <c r="K3">
-        <v>-0.327</v>
+        <v>-0.863</v>
       </c>
       <c r="L3">
-        <v>-3.27</v>
+        <v>-0.9535911602209944</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +743,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.972</v>
+        <v>0.323</v>
       </c>
       <c r="V3">
-        <v>0.09084112149532711</v>
+        <v>0.05676625659050966</v>
+      </c>
+      <c r="W3">
+        <v>-0.9442013129102844</v>
       </c>
       <c r="X3">
-        <v>0.07693205798252749</v>
+        <v>0.1340078015242971</v>
+      </c>
+      <c r="Y3">
+        <v>-1.078209114434582</v>
       </c>
       <c r="AB3">
-        <v>0.07670751935730633</v>
+        <v>0.1308060524157124</v>
       </c>
       <c r="AD3">
-        <v>0.051</v>
+        <v>0.228</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.051</v>
+        <v>0.228</v>
       </c>
       <c r="AG3">
-        <v>-0.9209999999999999</v>
+        <v>-0.095</v>
       </c>
       <c r="AH3">
-        <v>0.004743744767928565</v>
+        <v>0.03852652923284894</v>
       </c>
       <c r="AI3">
-        <v>0.05284974093264248</v>
+        <v>0.1289592760180996</v>
       </c>
       <c r="AJ3">
-        <v>-0.09418140914203905</v>
+        <v>-0.01697944593386953</v>
       </c>
       <c r="AK3">
-        <v>131.5714285714305</v>
+        <v>-0.06574394463667819</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AN3">
-        <v>-0.1895910780669145</v>
+        <v>-0.3019867549668874</v>
       </c>
       <c r="AO3">
-        <v>-53.16666666666666</v>
+        <v>-68.81818181818183</v>
       </c>
       <c r="AP3">
-        <v>3.423791821561338</v>
+        <v>0.1258278145695364</v>
       </c>
       <c r="AQ3">
-        <v>-53.16666666666666</v>
+        <v>-68.81818181818183</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_electronics_general.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.6662983425414364</v>
+        <v>-0.295959595959596</v>
       </c>
       <c r="H2">
-        <v>-0.6751381215469613</v>
+        <v>-0.3373737373737374</v>
       </c>
       <c r="I2">
-        <v>-0.8364640883977901</v>
+        <v>-0.2005050505050505</v>
       </c>
       <c r="J2">
-        <v>-0.8364640883977901</v>
+        <v>-0.2005050505050505</v>
       </c>
       <c r="K2">
-        <v>-0.863</v>
+        <v>-0.539</v>
       </c>
       <c r="L2">
-        <v>-0.9535911602209944</v>
+        <v>-0.2722222222222223</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,64 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.323</v>
+        <v>0.098</v>
       </c>
       <c r="V2">
-        <v>0.05676625659050966</v>
+        <v>0.03081761006289308</v>
       </c>
       <c r="W2">
-        <v>-0.9442013129102844</v>
+        <v>-0.35</v>
       </c>
       <c r="X2">
-        <v>0.1340078015242971</v>
+        <v>0.1121940423174274</v>
       </c>
       <c r="Y2">
-        <v>-1.078209114434582</v>
+        <v>-0.4621940423174274</v>
+      </c>
+      <c r="Z2">
+        <v>6.947368421052628</v>
+      </c>
+      <c r="AA2">
+        <v>-1.39298245614035</v>
       </c>
       <c r="AB2">
-        <v>0.1308060524157124</v>
+        <v>0.1105313994934426</v>
+      </c>
+      <c r="AC2">
+        <v>-1.503513855633793</v>
       </c>
       <c r="AD2">
-        <v>0.228</v>
+        <v>0.083</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.228</v>
+        <v>0.083</v>
       </c>
       <c r="AG2">
-        <v>-0.095</v>
+        <v>-0.015</v>
       </c>
       <c r="AH2">
-        <v>0.03852652923284894</v>
+        <v>0.02543671467974257</v>
       </c>
       <c r="AI2">
-        <v>0.1289592760180996</v>
+        <v>0.05958363244795406</v>
       </c>
       <c r="AJ2">
-        <v>-0.01697944593386953</v>
+        <v>-0.004739336492890995</v>
       </c>
       <c r="AK2">
-        <v>-0.06574394463667819</v>
+        <v>-0.01158301158301158</v>
       </c>
       <c r="AL2">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="AM2">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="AN2">
-        <v>-0.3019867549668874</v>
+        <v>-0.2189973614775726</v>
       </c>
       <c r="AO2">
-        <v>-68.81818181818183</v>
+        <v>-26.46666666666667</v>
       </c>
       <c r="AP2">
-        <v>0.1258278145695364</v>
+        <v>0.03957783641160949</v>
       </c>
       <c r="AQ2">
-        <v>-68.81818181818183</v>
+        <v>-26.46666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -704,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.6662983425414364</v>
+        <v>-0.295959595959596</v>
       </c>
       <c r="H3">
-        <v>-0.6751381215469613</v>
+        <v>-0.3373737373737374</v>
       </c>
       <c r="I3">
-        <v>-0.8364640883977901</v>
+        <v>-0.2005050505050505</v>
       </c>
       <c r="J3">
-        <v>-0.8364640883977901</v>
+        <v>-0.2005050505050505</v>
       </c>
       <c r="K3">
-        <v>-0.863</v>
+        <v>-0.539</v>
       </c>
       <c r="L3">
-        <v>-0.9535911602209944</v>
+        <v>-0.2722222222222223</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,64 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.323</v>
+        <v>0.098</v>
       </c>
       <c r="V3">
-        <v>0.05676625659050966</v>
+        <v>0.03081761006289308</v>
       </c>
       <c r="W3">
-        <v>-0.9442013129102844</v>
+        <v>-0.35</v>
       </c>
       <c r="X3">
-        <v>0.1340078015242971</v>
+        <v>0.1121940423174274</v>
       </c>
       <c r="Y3">
-        <v>-1.078209114434582</v>
+        <v>-0.4621940423174274</v>
+      </c>
+      <c r="Z3">
+        <v>6.947368421052628</v>
+      </c>
+      <c r="AA3">
+        <v>-1.39298245614035</v>
       </c>
       <c r="AB3">
-        <v>0.1308060524157124</v>
+        <v>0.1105313994934426</v>
+      </c>
+      <c r="AC3">
+        <v>-1.503513855633793</v>
       </c>
       <c r="AD3">
-        <v>0.228</v>
+        <v>0.083</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.228</v>
+        <v>0.083</v>
       </c>
       <c r="AG3">
-        <v>-0.095</v>
+        <v>-0.015</v>
       </c>
       <c r="AH3">
-        <v>0.03852652923284894</v>
+        <v>0.02543671467974257</v>
       </c>
       <c r="AI3">
-        <v>0.1289592760180996</v>
+        <v>0.05958363244795406</v>
       </c>
       <c r="AJ3">
-        <v>-0.01697944593386953</v>
+        <v>-0.004739336492890995</v>
       </c>
       <c r="AK3">
-        <v>-0.06574394463667819</v>
+        <v>-0.01158301158301158</v>
       </c>
       <c r="AL3">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="AM3">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="AN3">
-        <v>-0.3019867549668874</v>
+        <v>-0.2189973614775726</v>
       </c>
       <c r="AO3">
-        <v>-68.81818181818183</v>
+        <v>-26.46666666666667</v>
       </c>
       <c r="AP3">
-        <v>0.1258278145695364</v>
+        <v>0.03957783641160949</v>
       </c>
       <c r="AQ3">
-        <v>-68.81818181818183</v>
+        <v>-26.46666666666667</v>
       </c>
     </row>
   </sheetData>
